--- a/словари/криминал.xlsx
+++ b/словари/криминал.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EA247D-5E23-45ED-98AA-18DC668825F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76388B7E-576D-46D3-85A0-745B786F2950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="неизменные_короткие" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>форма таких «рецензий» иногда немного напрягала</t>
   </si>
@@ -44,6 +44,84 @@
   </si>
   <si>
     <t>директора торговых учреждений</t>
+  </si>
+  <si>
+    <t>брежневской (застойной) конституцией</t>
+  </si>
+  <si>
+    <t>брежневским (застойный) постановлением</t>
+  </si>
+  <si>
+    <t>разговор Гена</t>
+  </si>
+  <si>
+    <t>разговор Генa</t>
+  </si>
+  <si>
+    <t>разрешил Гена</t>
+  </si>
+  <si>
+    <t>разрешил Генa</t>
+  </si>
+  <si>
+    <t>выразился Гена</t>
+  </si>
+  <si>
+    <t>выразился Генa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Атлангериег </t>
+  </si>
+  <si>
+    <t>Атлангериев</t>
+  </si>
+  <si>
+    <t>аттракционы Центральном парке культур</t>
+  </si>
+  <si>
+    <t>аттракционы в Центральном парке культур</t>
+  </si>
+  <si>
+    <t>знакомый Гена</t>
+  </si>
+  <si>
+    <t>знакомый Генa</t>
+  </si>
+  <si>
+    <t>В «лазанской» группировке</t>
+  </si>
+  <si>
+    <t>В «лазанском» преступном сообществе</t>
+  </si>
+  <si>
+    <t>как Гена</t>
+  </si>
+  <si>
+    <t>как Генa</t>
+  </si>
+  <si>
+    <t>«лазанской» группировки</t>
+  </si>
+  <si>
+    <t>«лазанского» преступного сообщества</t>
+  </si>
+  <si>
+    <t>Гена Шрам</t>
+  </si>
+  <si>
+    <t>Генa Шрам</t>
+  </si>
+  <si>
+    <t>Если бы Гена</t>
+  </si>
+  <si>
+    <t>Если бы Генa</t>
+  </si>
+  <si>
+    <t>и Гена</t>
+  </si>
+  <si>
+    <t>и Генa</t>
   </si>
 </sst>
 </file>
@@ -361,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="52.453125" customWidth="1"/>
@@ -376,6 +454,94 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -383,7 +549,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B3B0CB-2BD5-4EB9-9DB0-6C22865F1CAF}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="45.6328125" customWidth="1"/>
@@ -403,6 +569,22 @@
         <v>4</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/словари/криминал.xlsx
+++ b/словари/криминал.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76388B7E-576D-46D3-85A0-745B786F2950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE52357-1A76-4332-974E-D0F5EF57F065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="неизменные_короткие" sheetId="1" r:id="rId1"/>
-    <sheet name="ошибки" sheetId="2" r:id="rId2"/>
+    <sheet name="неизменные" sheetId="3" r:id="rId2"/>
+    <sheet name="ошибки" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>форма таких «рецензий» иногда немного напрягала</t>
   </si>
@@ -122,6 +123,21 @@
   </si>
   <si>
     <t>и Генa</t>
+  </si>
+  <si>
+    <t>Гены Шрама</t>
+  </si>
+  <si>
+    <t>«лазанская» группировка</t>
+  </si>
+  <si>
+    <t>«лазанское» преступное сообщество</t>
+  </si>
+  <si>
+    <t>могущественной чеченской преступной группировки</t>
+  </si>
+  <si>
+    <t>могущественного чеченского преступного сообщества</t>
   </si>
 </sst>
 </file>
@@ -439,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="52.453125" customWidth="1"/>
@@ -542,12 +558,46 @@
         <v>30</v>
       </c>
     </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003C73B8-E647-489E-B76A-27BE5419F554}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B3B0CB-2BD5-4EB9-9DB0-6C22865F1CAF}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/словари/криминал.xlsx
+++ b/словари/криминал.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE52357-1A76-4332-974E-D0F5EF57F065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28BD523-EA85-4112-9AAD-7EFADA1C2AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>форма таких «рецензий» иногда немного напрягала</t>
   </si>
@@ -138,6 +138,12 @@
   </si>
   <si>
     <t>могущественного чеченского преступного сообщества</t>
+  </si>
+  <si>
+    <t>одиннадцатую секцию торговой точки «Автомобили», через которую</t>
+  </si>
+  <si>
+    <t>одиннадцатый раздел торговой точки «Автомобили», через который</t>
   </si>
 </sst>
 </file>
@@ -581,8 +587,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003C73B8-E647-489E-B76A-27BE5419F554}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="60.90625" customWidth="1"/>
+    <col min="2" max="2" width="52.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -590,6 +600,14 @@
       </c>
       <c r="B1" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/словари/криминал.xlsx
+++ b/словари/криминал.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E28BD523-EA85-4112-9AAD-7EFADA1C2AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57330ED-1300-4631-B3EA-603C6371FAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="неизменные_короткие" sheetId="1" r:id="rId1"/>
     <sheet name="неизменные" sheetId="3" r:id="rId2"/>
-    <sheet name="ошибки" sheetId="2" r:id="rId3"/>
+    <sheet name="неизменные_длинные" sheetId="4" r:id="rId3"/>
+    <sheet name="ошибки" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
   <si>
     <t>форма таких «рецензий» иногда немного напрягала</t>
   </si>
@@ -144,19 +145,90 @@
   </si>
   <si>
     <t>одиннадцатый раздел торговой точки «Автомобили», через который</t>
+  </si>
+  <si>
+    <t>авторитет же чеченцев возрастал</t>
+  </si>
+  <si>
+    <t>личная значимость же чеченцев возрастала</t>
+  </si>
+  <si>
+    <t>позвонил ресторан</t>
+  </si>
+  <si>
+    <t>позвонил в ресторан</t>
+  </si>
+  <si>
+    <t>несших «боевую вахту» у кафе</t>
+  </si>
+  <si>
+    <t>нёсших «боевую вахту» у закусочной</t>
+  </si>
+  <si>
+    <t>Тактика чеченской общины строилась</t>
+  </si>
+  <si>
+    <t>Под-ход чеченской общины строился</t>
+  </si>
+  <si>
+    <t>«лазанской» группировке</t>
+  </si>
+  <si>
+    <t>«лазанском» преступном сообществе</t>
+  </si>
+  <si>
+    <t>депорт</t>
+  </si>
+  <si>
+    <t>департ</t>
+  </si>
+  <si>
+    <t>чеченская группировка, вначале малочисленная и плохо организованная, умышленно выводилась</t>
+  </si>
+  <si>
+    <t>чеченское преступное со-общество, в-начале мало-численное и плохо со-гласованное, умышленно вы-водилось</t>
+  </si>
+  <si>
+    <t>опасной из них является так называемая чеченская группа, совершающая</t>
+  </si>
+  <si>
+    <t>опасным из них является так на-зываемое чеченское под-раз-деление, совершающее</t>
+  </si>
+  <si>
+    <t>своих сообщнике</t>
+  </si>
+  <si>
+    <t>своих сообщников</t>
+  </si>
+  <si>
+    <t>группа московских боевиков избила</t>
+  </si>
+  <si>
+    <t>под-раз-деление московских бое-виков из-било</t>
+  </si>
+  <si>
+    <t>в программе «Время»</t>
+  </si>
+  <si>
+    <t>в быдло-показе «Время»</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="LiberEmb"/>
     </font>
   </fonts>
   <fills count="2">
@@ -179,8 +251,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -461,14 +534,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="52.453125" customWidth="1"/>
     <col min="2" max="2" width="66.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -476,7 +549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -484,7 +557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -492,7 +565,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -500,7 +573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -508,7 +581,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -516,7 +589,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -524,7 +597,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -532,7 +605,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -540,7 +613,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -548,7 +621,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -556,7 +629,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -564,7 +637,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -572,12 +645,60 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>32</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -587,14 +708,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{003C73B8-E647-489E-B76A-27BE5419F554}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="60.90625" customWidth="1"/>
-    <col min="2" max="2" width="52.81640625" customWidth="1"/>
+    <col min="1" max="1" width="74.1796875" customWidth="1"/>
+    <col min="2" max="2" width="71.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>34</v>
       </c>
@@ -602,12 +723,20 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>36</v>
       </c>
       <c r="B2" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -616,20 +745,42 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CDED786-61B5-47B9-AC80-CC0CC562BAE8}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="123.81640625" customWidth="1"/>
+    <col min="2" max="2" width="119.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.5">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B3B0CB-2BD5-4EB9-9DB0-6C22865F1CAF}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="45.6328125" customWidth="1"/>
     <col min="2" max="2" width="44.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -637,7 +788,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -645,12 +796,36 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/словари/криминал.xlsx
+++ b/словари/криминал.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57330ED-1300-4631-B3EA-603C6371FAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17214A5C-03D9-46E0-A048-90C53888B92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57490" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>форма таких «рецензий» иногда немного напрягала</t>
   </si>
@@ -211,13 +211,25 @@
   </si>
   <si>
     <t>в быдло-показе «Время»</t>
+  </si>
+  <si>
+    <t>микроклимат Бутырки подействовал</t>
+  </si>
+  <si>
+    <t>внутренние погодные условия Бутырки подействовали</t>
+  </si>
+  <si>
+    <t>«таганской» версии</t>
+  </si>
+  <si>
+    <t>«таганскому» исполнению</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,6 +241,13 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="LiberEmb"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -251,9 +270,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -534,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="52.453125" customWidth="1"/>
@@ -699,6 +719,22 @@
       </c>
       <c r="B20" t="s">
         <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
